--- a/bi/tkDashboard/PID/docs/PID销售趋势映射表.xlsx
+++ b/bi/tkDashboard/PID/docs/PID销售趋势映射表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="24460" activeTab="1"/>
+    <workbookView windowHeight="23960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="源数据路径" sheetId="2" r:id="rId1"/>
@@ -380,7 +380,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="177">
   <si>
     <t>序号</t>
   </si>
@@ -791,7 +791,7 @@
     <t>总GMV</t>
   </si>
   <si>
-    <t>财务GMV</t>
+    <t>财务GMV（在线excel的净利润）</t>
   </si>
   <si>
     <t>product_list-》ID</t>
@@ -1188,6 +1188,9 @@
   </si>
   <si>
     <t>总GMV=营业总额-商家折扣+运费</t>
+  </si>
+  <si>
+    <t>财务GMV</t>
   </si>
   <si>
     <t>筛选"Cancelation/Return Type"不为Cancel，"Order Amount"不为0，根据PID计算Quantity
@@ -2139,7 +2142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2220,12 +2223,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2836,7 +2833,7 @@
     </row>
     <row r="5" ht="349.6" spans="1:6">
       <c r="A5" s="24"/>
-      <c r="B5" s="29"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" t="s">
         <v>8</v>
@@ -2872,7 +2869,7 @@
     </row>
     <row r="7" ht="317.9" spans="1:6">
       <c r="A7" s="24"/>
-      <c r="B7" s="29"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="26"/>
       <c r="D7" t="s">
         <v>8</v>
@@ -2908,7 +2905,7 @@
     </row>
     <row r="9" ht="260.4" spans="1:6">
       <c r="A9" s="24"/>
-      <c r="B9" s="29"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="26"/>
       <c r="D9" t="s">
         <v>8</v>
@@ -2925,10 +2922,10 @@
       <c r="A10" s="24">
         <v>5</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="27" t="s">
         <v>5</v>
       </c>
       <c r="D10" t="s">
@@ -2945,7 +2942,7 @@
     <row r="11" ht="268.85" spans="1:6">
       <c r="A11" s="24"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="30"/>
+      <c r="C11" s="27"/>
       <c r="D11" t="s">
         <v>8</v>
       </c>
@@ -3073,7 +3070,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="4" customFormat="1" ht="34" spans="1:9">
+    <row r="5" s="4" customFormat="1" ht="17" spans="1:9">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="s">
@@ -3092,7 +3089,7 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
         <v>36</v>
@@ -3113,7 +3110,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
         <v>39</v>
@@ -3134,7 +3131,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="B8" s="10" t="s">
         <v>35</v>
       </c>
@@ -3154,7 +3151,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
         <v>35</v>
@@ -3175,7 +3172,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A10" s="10"/>
       <c r="B10" s="10" t="s">
         <v>35</v>
@@ -3196,7 +3193,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
         <v>50</v>
@@ -3219,7 +3216,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
         <v>50</v>
@@ -3242,7 +3239,7 @@
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
         <v>50</v>
@@ -3265,7 +3262,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
         <v>50</v>
@@ -3288,7 +3285,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>50</v>
@@ -3311,7 +3308,7 @@
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
         <v>50</v>
@@ -3334,7 +3331,7 @@
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A17" s="14" t="s">
         <v>63</v>
       </c>
@@ -3351,7 +3348,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
@@ -3368,7 +3365,7 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="19" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -3385,7 +3382,7 @@
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="20" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A20" s="10"/>
       <c r="B20" s="10" t="s">
         <v>50</v>
@@ -3408,7 +3405,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="21" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
         <v>50</v>
@@ -3431,7 +3428,7 @@
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="22" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A22" s="10" t="s">
         <v>72</v>
       </c>
@@ -3448,7 +3445,7 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="23" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
         <v>50</v>
@@ -3471,7 +3468,7 @@
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="24" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
         <v>50</v>
@@ -3517,7 +3514,7 @@
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="26" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
         <v>50</v>
@@ -3540,7 +3537,7 @@
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="27" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
         <v>50</v>
@@ -3563,7 +3560,7 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="28" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
         <v>50</v>
@@ -3586,7 +3583,7 @@
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="29" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
         <v>50</v>
@@ -3609,7 +3606,7 @@
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="30" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>50</v>
@@ -3632,7 +3629,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="31" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A31" s="10" t="s">
         <v>88</v>
       </c>
@@ -3649,7 +3646,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="32" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>50</v>
@@ -3672,7 +3669,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="33" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
         <v>50</v>
@@ -3695,7 +3692,7 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="34" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
         <v>50</v>
@@ -3718,7 +3715,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="35" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
         <v>50</v>
@@ -3741,7 +3738,7 @@
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="36" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
         <v>50</v>
@@ -3764,7 +3761,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="37" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
         <v>50</v>
@@ -3787,7 +3784,7 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="38" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
         <v>50</v>
@@ -3810,7 +3807,7 @@
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="39" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
         <v>50</v>
@@ -3833,7 +3830,7 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="40" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A40" s="10" t="s">
         <v>106</v>
       </c>
@@ -3850,7 +3847,7 @@
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="41" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
         <v>50</v>
@@ -3873,7 +3870,7 @@
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="42" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
         <v>50</v>
@@ -3919,7 +3916,7 @@
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="44" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A44" s="10"/>
       <c r="B44" s="10" t="s">
         <v>50</v>
@@ -3942,7 +3939,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="45" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
         <v>50</v>
@@ -3965,7 +3962,7 @@
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="34" spans="1:9">
+    <row r="46" s="1" customFormat="1" ht="17" spans="1:9">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
         <v>50</v>
@@ -3988,7 +3985,7 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" ht="34" spans="1:9">
+    <row r="47" ht="17" spans="1:9">
       <c r="A47" s="10" t="s">
         <v>118</v>
       </c>
@@ -4011,7 +4008,7 @@
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" ht="34" spans="1:9">
+    <row r="48" ht="17" spans="1:9">
       <c r="A48" s="10" t="s">
         <v>122</v>
       </c>
@@ -4034,7 +4031,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" ht="34" spans="1:9">
+    <row r="49" ht="17" spans="1:9">
       <c r="A49" s="10" t="s">
         <v>124</v>
       </c>
@@ -4115,7 +4112,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
     </row>
-    <row r="53" ht="34" spans="1:9">
+    <row r="53" ht="17" spans="1:9">
       <c r="A53" s="10" t="s">
         <v>134</v>
       </c>
@@ -4132,7 +4129,7 @@
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" ht="34" spans="1:9">
+    <row r="54" ht="17" spans="1:9">
       <c r="A54" s="10" t="s">
         <v>136</v>
       </c>
@@ -4151,7 +4148,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" ht="34" spans="1:9">
+    <row r="55" ht="17" spans="1:9">
       <c r="A55" s="10"/>
       <c r="B55" s="10" t="s">
         <v>138</v>
@@ -4170,7 +4167,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" ht="84" spans="1:9">
+    <row r="56" ht="51" spans="1:9">
       <c r="A56" s="22" t="s">
         <v>140</v>
       </c>
@@ -4193,7 +4190,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" ht="84" spans="1:9">
+    <row r="57" ht="51" spans="1:9">
       <c r="A57" s="22" t="s">
         <v>144</v>
       </c>
@@ -4216,7 +4213,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="58" ht="135" spans="1:9">
+    <row r="58" ht="84" spans="1:9">
       <c r="A58" s="22" t="s">
         <v>148</v>
       </c>
@@ -4239,7 +4236,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" ht="34" spans="1:9">
+    <row r="59" ht="17" spans="1:9">
       <c r="A59" s="23" t="s">
         <v>152</v>
       </c>
@@ -4249,12 +4246,12 @@
         <v>43</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" ht="51" spans="1:9">
       <c r="A60" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>35</v>
@@ -4263,21 +4260,21 @@
         <v>20</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="61" ht="101" spans="1:9">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" ht="68" spans="1:9">
       <c r="A61" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>35</v>
@@ -4286,21 +4283,21 @@
         <v>20</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" ht="68" spans="1:9">
       <c r="A62" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>35</v>
@@ -4321,9 +4318,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" ht="34" spans="1:9">
+    <row r="63" ht="17" spans="1:9">
       <c r="A63" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -4333,12 +4330,12 @@
         <v>43</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" ht="68" spans="1:9">
       <c r="A64" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>35</v>
@@ -4347,21 +4344,21 @@
         <v>20</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="65" ht="34" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" ht="17" spans="1:7">
       <c r="A65" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -4397,37 +4394,37 @@
   <sheetData>
     <row r="1" ht="17" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" ht="101" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" ht="135" spans="1:1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" ht="118" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" ht="135" spans="1:1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" ht="118" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
